--- a/xls/square_16_tri3_10.xlsx
+++ b/xls/square_16_tri3_10.xlsx
@@ -482,13 +482,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>2.804926166189483</v>
+        <v>2.8049261488831854</v>
       </c>
       <c r="J10">
-        <v>-0.31219841983611324</v>
+        <v>-0.3121984418252911</v>
       </c>
       <c r="K10">
-        <v>0.5677753452808607</v>
+        <v>0.567775303040348</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -517,13 +517,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-2.011843541813478</v>
+        <v>-2.0118439474075114</v>
       </c>
       <c r="J11">
-        <v>-1.966475818475726</v>
+        <v>-1.9664760208111756</v>
       </c>
       <c r="K11">
-        <v>-1.2433652577588137</v>
+        <v>-1.243365127371887</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -552,13 +552,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-1.9964973599812617</v>
+        <v>-1.996496382716754</v>
       </c>
       <c r="J12">
-        <v>-2.0064556577353305</v>
+        <v>-2.0064547993425697</v>
       </c>
       <c r="K12">
-        <v>-1.3173677267028885</v>
+        <v>-1.3173675161794454</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -587,13 +587,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>-2.010050014850554</v>
+        <v>-2.010049995150648</v>
       </c>
       <c r="J13">
-        <v>-1.8397596435927666</v>
+        <v>-1.839759579030564</v>
       </c>
       <c r="K13">
-        <v>-0.8267808069445475</v>
+        <v>-0.8267806180746803</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -622,13 +622,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-1.9767958302539728</v>
+        <v>-1.9767960945103646</v>
       </c>
       <c r="J14">
-        <v>-1.8923013718380024</v>
+        <v>-1.892301499985945</v>
       </c>
       <c r="K14">
-        <v>-0.8960865098718782</v>
+        <v>-0.8960862711619667</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -657,13 +657,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-1.715652771221527</v>
+        <v>-1.715652833887263</v>
       </c>
       <c r="J15">
-        <v>-1.3763047600037523</v>
+        <v>-1.3763047797581478</v>
       </c>
       <c r="K15">
-        <v>-0.2519427693080623</v>
+        <v>-0.2519427214506912</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -692,13 +692,13 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>-1.3522750384404603</v>
+        <v>-1.3522751773428934</v>
       </c>
       <c r="J16">
-        <v>-1.0935944689047854</v>
+        <v>-1.093594503314489</v>
       </c>
       <c r="K16">
-        <v>-0.01928114477652741</v>
+        <v>-0.019281145090347812</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1734</v>
       </c>
       <c r="I17">
-        <v>-0.5092305184508003</v>
+        <v>-0.5092304747841888</v>
       </c>
       <c r="J17">
-        <v>-0.34798339553459007</v>
+        <v>-0.34798337783650707</v>
       </c>
       <c r="K17">
-        <v>2.5373099559975825</v>
+        <v>2.5373099754477457</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1944</v>
       </c>
       <c r="I18">
-        <v>-0.2756715171665848</v>
+        <v>-0.27567154440140135</v>
       </c>
       <c r="J18">
-        <v>-0.22244408503583463</v>
+        <v>-0.222444104489015</v>
       </c>
       <c r="K18">
-        <v>3.297863961568927</v>
+        <v>3.2978640623944044</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -797,13 +797,13 @@
         <v>2166</v>
       </c>
       <c r="I19">
-        <v>-0.0002639171682211406</v>
+        <v>-0.0002639171682340222</v>
       </c>
       <c r="J19">
-        <v>-0.00025648458147792095</v>
+        <v>-0.00025648458149490314</v>
       </c>
       <c r="K19">
-        <v>2.6414563890381757</v>
+        <v>2.6414563889111986</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -832,13 +832,13 @@
         <v>2400</v>
       </c>
       <c r="I20">
-        <v>-0.00023088333966123615</v>
+        <v>-0.00023088333960884534</v>
       </c>
       <c r="J20">
-        <v>-0.00018566220419295843</v>
+        <v>-0.0001856622041555265</v>
       </c>
       <c r="K20">
-        <v>2.505422717446859</v>
+        <v>2.50542271737764</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -867,13 +867,13 @@
         <v>2646</v>
       </c>
       <c r="I21">
-        <v>-0.00013845224616763842</v>
+        <v>-0.0001384522461741497</v>
       </c>
       <c r="J21">
-        <v>-9.336371374219812e-5</v>
+        <v>-9.336371374451302e-5</v>
       </c>
       <c r="K21">
-        <v>2.2574072950666304</v>
+        <v>2.257407295084654</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -902,13 +902,13 @@
         <v>2904</v>
       </c>
       <c r="I22">
-        <v>-5.398941668223739e-6</v>
+        <v>-5.3989416680790875e-6</v>
       </c>
       <c r="J22">
-        <v>-6.048265864264573e-6</v>
+        <v>-6.0482658644092245e-6</v>
       </c>
       <c r="K22">
-        <v>1.869094525340389</v>
+        <v>1.869094525588433</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -937,13 +937,13 @@
         <v>3174</v>
       </c>
       <c r="I23">
-        <v>-1.9842048744635814e-5</v>
+        <v>-1.9842048744250065e-5</v>
       </c>
       <c r="J23">
-        <v>-1.599507174208191e-5</v>
+        <v>-1.5995071741985472e-5</v>
       </c>
       <c r="K23">
-        <v>1.9834500194432443</v>
+        <v>1.9834500196752427</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -975,10 +975,10 @@
         <v>-2.9027111414166494e-6</v>
       </c>
       <c r="J24">
-        <v>-3.956547936971453e-6</v>
+        <v>-3.956547937260754e-6</v>
       </c>
       <c r="K24">
-        <v>1.8163544403348908</v>
+        <v>1.8163544401320002</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1007,13 +1007,13 @@
         <v>3750</v>
       </c>
       <c r="I25">
-        <v>2.625794157547796e-6</v>
+        <v>2.6257941574513637e-6</v>
       </c>
       <c r="J25">
-        <v>-4.308514023107036e-7</v>
+        <v>-4.308514025035693e-7</v>
       </c>
       <c r="K25">
-        <v>1.7636230097273369</v>
+        <v>1.7636230096229693</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1042,13 +1042,13 @@
         <v>4056</v>
       </c>
       <c r="I26">
-        <v>-5.6568327271295025e-6</v>
+        <v>-5.656832726743766e-6</v>
       </c>
       <c r="J26">
-        <v>-6.310384813300724e-6</v>
+        <v>-6.310384813397158e-6</v>
       </c>
       <c r="K26">
-        <v>1.8824953266270537</v>
+        <v>1.8824953266613722</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1080,10 +1080,10 @@
         <v>2.268219986714416e-6</v>
       </c>
       <c r="J27">
-        <v>-1.2793584888284224e-7</v>
+        <v>-1.279358486417603e-7</v>
       </c>
       <c r="K27">
-        <v>1.6954038930395074</v>
+        <v>1.6954038932314903</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1112,13 +1112,13 @@
         <v>4704</v>
       </c>
       <c r="I28">
-        <v>-3.505092670602084e-6</v>
+        <v>-3.5050926707467345e-6</v>
       </c>
       <c r="J28">
-        <v>-3.4127645203607626e-6</v>
+        <v>-3.4127645201678957e-6</v>
       </c>
       <c r="K28">
-        <v>1.7167391518788864</v>
+        <v>1.7167391519279585</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1147,13 +1147,13 @@
         <v>5046</v>
       </c>
       <c r="I29">
-        <v>2.0380316478382473e-7</v>
+        <v>2.0380316488025745e-7</v>
       </c>
       <c r="J29">
-        <v>-2.5869080498003623e-7</v>
+        <v>-2.5869080473895424e-7</v>
       </c>
       <c r="K29">
-        <v>1.4157721995248498</v>
+        <v>1.4157721995606103</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1185,10 +1185,10 @@
         <v>-9.34756399532644e-7</v>
       </c>
       <c r="J30">
-        <v>-8.961866121196184e-7</v>
+        <v>-8.961866120231854e-7</v>
       </c>
       <c r="K30">
-        <v>1.42449689467868</v>
+        <v>1.4244968947464853</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1217,13 +1217,13 @@
         <v>5766</v>
       </c>
       <c r="I31">
-        <v>-2.677309156520311e-7</v>
+        <v>-2.677309155555983e-7</v>
       </c>
       <c r="J31">
         <v>-3.2828691127525294e-7</v>
       </c>
       <c r="K31">
-        <v>1.2640000094461417</v>
+        <v>1.2640000096052677</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1252,13 +1252,13 @@
         <v>6144</v>
       </c>
       <c r="I32">
-        <v>-4.184772688496516e-7</v>
+        <v>-4.1847726875321877e-7</v>
       </c>
       <c r="J32">
-        <v>-3.9623554953661835e-7</v>
+        <v>-3.962355496812676e-7</v>
       </c>
       <c r="K32">
-        <v>1.2453546845745609</v>
+        <v>1.245354684368408</v>
       </c>
     </row>
   </sheetData>

--- a/xls/square_16_tri3_10.xlsx
+++ b/xls/square_16_tri3_10.xlsx
@@ -456,6 +456,76 @@
         <v>10</v>
       </c>
     </row>
+    <row r="8" spans="1:11">
+      <c r="A8" t="s">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>121</v>
+      </c>
+      <c r="C8" t="s">
+        <v>11</v>
+      </c>
+      <c r="D8">
+        <v>289</v>
+      </c>
+      <c r="E8" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8">
+        <v>81</v>
+      </c>
+      <c r="G8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H8">
+        <v>384</v>
+      </c>
+      <c r="I8">
+        <v>20.687877934622836</v>
+      </c>
+      <c r="J8">
+        <v>7.223447663238053</v>
+      </c>
+      <c r="K8">
+        <v>7.6717716354789065</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9">
+        <v>121</v>
+      </c>
+      <c r="C9" t="s">
+        <v>11</v>
+      </c>
+      <c r="D9">
+        <v>289</v>
+      </c>
+      <c r="E9" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9">
+        <v>100</v>
+      </c>
+      <c r="G9" t="s">
+        <v>13</v>
+      </c>
+      <c r="H9">
+        <v>486</v>
+      </c>
+      <c r="I9">
+        <v>4.6243967564618265</v>
+      </c>
+      <c r="J9">
+        <v>0.9389097201140765</v>
+      </c>
+      <c r="K9">
+        <v>1.6407496417852776</v>
+      </c>
+    </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>11</v>
